--- a/data/trans_dic/P37A$vacunaempresa-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunaempresa-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,24</t>
+          <t>0,21; 1,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,64</t>
+          <t>0,07; 0,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,09</t>
+          <t>0,16; 1,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,66</t>
+          <t>0,17; 0,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,01</t>
+          <t>0,19; 0,94</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,51</t>
+          <t>0,54; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,09</t>
+          <t>0,85; 2,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,82</t>
+          <t>0,19; 0,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,08</t>
+          <t>1,83; 3,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,27 +882,27 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,66</t>
+          <t>0,63; 1,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,87</t>
+          <t>0,24; 0,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,57</t>
+          <t>2,42; 3,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,08</t>
+          <t>0,46; 1,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,63</t>
+          <t>0,84; 1,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,12</t>
+          <t>2,27; 3,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,91</t>
+          <t>1,35; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,02</t>
+          <t>2,24; 5,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,09</t>
+          <t>0,19; 2,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,74</t>
+          <t>3,87; 7,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,79</t>
+          <t>0,61; 2,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,13</t>
+          <t>1,32; 5,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,41</t>
+          <t>0,83; 3,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,59</t>
+          <t>5,07; 8,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,08</t>
+          <t>1,22; 2,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,71</t>
+          <t>2,19; 4,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,29</t>
+          <t>0,74; 2,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,59</t>
+          <t>4,76; 7,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,47</t>
+          <t>0,75; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,88</t>
+          <t>0,96; 1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,75</t>
+          <t>0,24; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,23</t>
+          <t>2,17; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,84</t>
+          <t>0,33; 0,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,27</t>
+          <t>0,6; 1,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,83</t>
+          <t>0,33; 0,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,65</t>
+          <t>2,64; 3,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,59; 1,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,41</t>
+          <t>0,85; 1,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,7</t>
+          <t>0,35; 0,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,3</t>
+          <t>2,57; 3,33</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>6054</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2039; 12775</t>
+          <t>2170; 12889</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6530</t>
+          <t>0; 6532</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6308</t>
+          <t>0; 5270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7830</t>
+          <t>0; 9209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>897; 8391</t>
+          <t>897; 7529</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1539,27 +1539,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1137; 8221</t>
+          <t>1344; 8794</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4561; 15438</t>
+          <t>3915; 15484</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7373</t>
+          <t>0; 5684</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5231</t>
+          <t>0; 5471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2247; 12788</t>
+          <t>2605; 13163</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>114960</t>
+          <t>120526</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8386; 25655</t>
+          <t>9167; 26489</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18016; 40977</t>
+          <t>16685; 40186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3965; 16982</t>
+          <t>3897; 17360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34040; 70653</t>
+          <t>40875; 70590</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3922; 15406</t>
+          <t>3961; 15373</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11606; 29258</t>
+          <t>11094; 29109</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4145; 17354</t>
+          <t>4703; 17682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45512; 79822</t>
+          <t>52469; 81159</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15235; 35293</t>
+          <t>15226; 35913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32206; 60807</t>
+          <t>31354; 60519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11083; 28933</t>
+          <t>11156; 28824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90039; 141311</t>
+          <t>99788; 141184</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35746</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>85629</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7434; 21575</t>
+          <t>7460; 22090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9964; 28977</t>
+          <t>10786; 28833</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1191; 11417</t>
+          <t>1042; 11657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25197; 50029</t>
+          <t>27541; 51246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3021; 13311</t>
+          <t>2896; 13132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5958; 23549</t>
+          <t>6052; 23079</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4756; 18734</t>
+          <t>4554; 17458</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33075; 56733</t>
+          <t>37284; 63027</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12699; 31681</t>
+          <t>12556; 30659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20166; 44253</t>
+          <t>20568; 46491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8026; 25050</t>
+          <t>8132; 24710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63647; 99250</t>
+          <t>68787; 102620</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24270; 48014</t>
+          <t>24584; 48567</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33950; 64393</t>
+          <t>32875; 63554</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8017; 25458</t>
+          <t>8188; 25004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67664; 111326</t>
+          <t>76225; 116610</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11597; 28389</t>
+          <t>10996; 28172</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21340; 44994</t>
+          <t>21177; 47275</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11062; 29447</t>
+          <t>11519; 29056</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89273; 133384</t>
+          <t>98433; 137782</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39283; 66045</t>
+          <t>39214; 68139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60235; 98268</t>
+          <t>59470; 98105</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23402; 48243</t>
+          <t>23946; 49313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>170364; 234777</t>
+          <t>186413; 241161</t>
         </is>
       </c>
     </row>
